--- a/chapters/05-pandas/Excel_Sample.xlsx
+++ b/chapters/05-pandas/Excel_Sample.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,26 +425,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>d</t>
         </is>
@@ -458,12 +463,15 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>2</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -472,15 +480,18 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
         <v>4</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>6</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -489,15 +500,18 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
         <v>8</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>9</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>10</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -506,15 +520,18 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
         <v>12</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>13</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>14</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>15</v>
       </c>
     </row>
